--- a/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-type-document-attache.xlsx
+++ b/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-type-document-attache.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3987" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3987" uniqueCount="381">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:22:25+00:00</t>
+    <t>2026-06-30T08:22:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -834,6 +834,10 @@
   </si>
   <si>
     <t>ED.thumbnail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ED-1:Thumbnails cannot contain their own thumbnails {thumbnail.empty()}
+</t>
   </si>
   <si>
     <t>Observation.statusCode</t>
@@ -7474,7 +7478,7 @@
         <v>74</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>74</v>
+        <v>267</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>74</v>
@@ -7482,10 +7486,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7511,10 +7515,10 @@
         <v>91</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -7545,7 +7549,7 @@
       </c>
       <c r="Y59" s="2"/>
       <c r="Z59" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>74</v>
@@ -7563,7 +7567,7 @@
         <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -7583,10 +7587,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7684,10 +7688,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7728,7 +7732,7 @@
         <v>74</v>
       </c>
       <c r="S61" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="T61" t="s" s="2">
         <v>74</v>
@@ -7787,10 +7791,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7890,10 +7894,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -7993,10 +7997,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8096,10 +8100,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8199,10 +8203,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8300,10 +8304,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8401,10 +8405,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8504,10 +8508,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8607,10 +8611,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8710,10 +8714,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8736,13 +8740,13 @@
         <v>74</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -8793,7 +8797,7 @@
         <v>74</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -8813,10 +8817,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8839,7 +8843,7 @@
         <v>74</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="L72" s="2"/>
       <c r="M72" s="2"/>
@@ -8872,7 +8876,7 @@
       </c>
       <c r="Y72" s="2"/>
       <c r="Z72" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>74</v>
@@ -8890,7 +8894,7 @@
         <v>74</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -8910,10 +8914,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -8936,7 +8940,7 @@
         <v>74</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L73" s="2"/>
       <c r="M73" s="2"/>
@@ -8989,7 +8993,7 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -9009,10 +9013,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9068,25 +9072,25 @@
       </c>
       <c r="Y74" s="2"/>
       <c r="Z74" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF74" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="AA74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF74" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -9106,10 +9110,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9135,7 +9139,7 @@
         <v>171</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="M75" s="2"/>
       <c r="N75" s="2"/>
@@ -9187,7 +9191,7 @@
         <v>74</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -9207,10 +9211,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9308,10 +9312,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9411,10 +9415,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9514,10 +9518,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9617,10 +9621,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9720,10 +9724,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9823,10 +9827,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -9924,10 +9928,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10025,10 +10029,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10056,7 +10060,7 @@
         <v>209</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M84" t="s" s="2">
         <v>210</v>
@@ -10130,10 +10134,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10231,10 +10235,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10332,10 +10336,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10435,10 +10439,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10536,10 +10540,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10639,10 +10643,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10740,10 +10744,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10837,10 +10841,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -10942,10 +10946,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -10973,7 +10977,7 @@
         <v>260</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="M93" t="s" s="2">
         <v>261</v>
@@ -11047,10 +11051,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -11142,7 +11146,7 @@
         <v>74</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>74</v>
+        <v>267</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>74</v>
@@ -11150,10 +11154,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11181,7 +11185,7 @@
         <v>214</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M95" t="s" s="2">
         <v>215</v>
@@ -11255,10 +11259,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11356,17 +11360,17 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E97" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F97" t="s" s="2">
         <v>80</v>
@@ -11384,11 +11388,11 @@
         <v>74</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L97" s="2"/>
       <c r="M97" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -11439,7 +11443,7 @@
         <v>74</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -11459,10 +11463,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -11487,13 +11491,13 @@
         <v>74</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -11544,7 +11548,7 @@
         <v>74</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -11564,10 +11568,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -11595,10 +11599,10 @@
         <v>171</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -11649,7 +11653,7 @@
         <v>74</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -11669,10 +11673,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -11772,10 +11776,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -11798,7 +11802,7 @@
         <v>74</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="L101" s="2"/>
       <c r="M101" s="2"/>
@@ -11831,25 +11835,25 @@
       </c>
       <c r="Y101" s="2"/>
       <c r="Z101" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AA101" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF101" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="AA101" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB101" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC101" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD101" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE101" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF101" t="s" s="2">
-        <v>335</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -11869,10 +11873,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -11895,7 +11899,7 @@
         <v>74</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="L102" s="2"/>
       <c r="M102" s="2"/>
@@ -11928,25 +11932,25 @@
       </c>
       <c r="Y102" s="2"/>
       <c r="Z102" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="AA102" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD102" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE102" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF102" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="AA102" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB102" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC102" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD102" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE102" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF102" t="s" s="2">
-        <v>337</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -11966,10 +11970,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -11996,7 +12000,7 @@
       </c>
       <c r="L103" s="2"/>
       <c r="M103" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -12047,7 +12051,7 @@
         <v>74</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -12067,10 +12071,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12093,7 +12097,7 @@
         <v>74</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L104" s="2"/>
       <c r="M104" s="2"/>
@@ -12146,7 +12150,7 @@
         <v>74</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -12166,10 +12170,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12192,7 +12196,7 @@
         <v>74</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L105" s="2"/>
       <c r="M105" s="2"/>
@@ -12245,7 +12249,7 @@
         <v>74</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -12265,10 +12269,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12291,7 +12295,7 @@
         <v>74</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L106" s="2"/>
       <c r="M106" s="2"/>
@@ -12344,7 +12348,7 @@
         <v>74</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -12364,10 +12368,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -12390,7 +12394,7 @@
         <v>74</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L107" s="2"/>
       <c r="M107" s="2"/>
@@ -12443,7 +12447,7 @@
         <v>74</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -12463,10 +12467,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -12489,7 +12493,7 @@
         <v>74</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L108" s="2"/>
       <c r="M108" s="2"/>
@@ -12542,7 +12546,7 @@
         <v>74</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -12562,10 +12566,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -12588,7 +12592,7 @@
         <v>74</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L109" s="2"/>
       <c r="M109" s="2"/>
@@ -12641,7 +12645,7 @@
         <v>74</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -12661,10 +12665,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -12687,7 +12691,7 @@
         <v>74</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L110" s="2"/>
       <c r="M110" s="2"/>
@@ -12740,7 +12744,7 @@
         <v>74</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -12760,10 +12764,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -12786,7 +12790,7 @@
         <v>74</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L111" s="2"/>
       <c r="M111" s="2"/>
@@ -12839,7 +12843,7 @@
         <v>74</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -12859,10 +12863,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -12885,7 +12889,7 @@
         <v>74</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L112" s="2"/>
       <c r="M112" s="2"/>
@@ -12938,7 +12942,7 @@
         <v>74</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -12958,10 +12962,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -12984,7 +12988,7 @@
         <v>74</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L113" s="2"/>
       <c r="M113" s="2"/>
@@ -13037,7 +13041,7 @@
         <v>74</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -13057,10 +13061,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -13083,11 +13087,11 @@
         <v>74</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="L114" s="2"/>
       <c r="M114" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -13138,7 +13142,7 @@
         <v>74</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -13158,10 +13162,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -13259,10 +13263,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -13360,10 +13364,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -13461,10 +13465,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -13562,10 +13566,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -13665,10 +13669,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -13768,10 +13772,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -13871,10 +13875,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -13974,10 +13978,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -14075,10 +14079,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -14112,7 +14116,7 @@
       </c>
       <c r="Q124" s="2"/>
       <c r="R124" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="S124" t="s" s="2">
         <v>74</v>
@@ -14134,7 +14138,7 @@
       </c>
       <c r="Y124" s="2"/>
       <c r="Z124" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AA124" t="s" s="2">
         <v>74</v>
@@ -14152,7 +14156,7 @@
         <v>74</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
@@ -14172,10 +14176,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -14198,7 +14202,7 @@
         <v>74</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L125" s="2"/>
       <c r="M125" s="2"/>
@@ -14251,7 +14255,7 @@
         <v>74</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>75</v>
@@ -14271,10 +14275,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -14297,7 +14301,7 @@
         <v>74</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="L126" s="2"/>
       <c r="M126" s="2"/>
@@ -14350,7 +14354,7 @@
         <v>74</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
